--- a/data/trans_dic/P37-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P37-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha vacunado de la gripe en la última campaña</t>
+          <t>Población que se ha vacunado de la gripe en la última campaña (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,93; 29,36</t>
+          <t>24,07; 29,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,74; 38,18</t>
+          <t>32,38; 38,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,81; 37,37</t>
+          <t>30,8; 37,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,44; 58,64</t>
+          <t>50,42; 59,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,1; 32,24</t>
+          <t>27,14; 32,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,92; 36,38</t>
+          <t>30,97; 36,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,17; 38,91</t>
+          <t>32,65; 38,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,93; 67,39</t>
+          <t>61,69; 67,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,56; 30,25</t>
+          <t>26,49; 30,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,16; 36,09</t>
+          <t>32,21; 36,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,47; 37,29</t>
+          <t>32,45; 37,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,32; 63,03</t>
+          <t>58,22; 63,16</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,41</t>
+          <t>5,76; 8,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 12,31</t>
+          <t>9,24; 12,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,07; 11,75</t>
+          <t>9,12; 11,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,27; 25,2</t>
+          <t>15,22; 25,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,68</t>
+          <t>5,06; 7,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,51</t>
+          <t>7,55; 10,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 11,73</t>
+          <t>8,86; 11,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,08; 50,53</t>
+          <t>25,12; 49,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 7,55</t>
+          <t>5,78; 7,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 10,93</t>
+          <t>8,88; 10,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,29; 11,25</t>
+          <t>9,3; 11,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,79; 38,05</t>
+          <t>22,62; 38,33</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 14,26</t>
+          <t>8,63; 14,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 14,89</t>
+          <t>8,0; 14,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 14,08</t>
+          <t>7,98; 13,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,26; 37,2</t>
+          <t>29,59; 37,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 12,49</t>
+          <t>7,01; 12,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 12,39</t>
+          <t>6,58; 12,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 13,16</t>
+          <t>7,62; 13,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,02; 34,08</t>
+          <t>28,02; 34,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 12,74</t>
+          <t>8,68; 12,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 12,43</t>
+          <t>7,95; 12,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 12,78</t>
+          <t>8,62; 12,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,61; 34,78</t>
+          <t>29,91; 34,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,68; 14,97</t>
+          <t>12,76; 14,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,37; 19,14</t>
+          <t>16,4; 19,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 17,04</t>
+          <t>14,53; 16,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,37; 31,83</t>
+          <t>22,18; 31,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 17,08</t>
+          <t>14,63; 17,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,02; 19,75</t>
+          <t>16,96; 19,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,98; 18,57</t>
+          <t>15,96; 18,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,66; 50,19</t>
+          <t>34,74; 50,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,07; 15,81</t>
+          <t>14,03; 15,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,01; 18,94</t>
+          <t>17,04; 18,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,56; 17,45</t>
+          <t>15,58; 17,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,59; 40,65</t>
+          <t>30,57; 40,77</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha vacunado de la gripe en la última campaña</t>
+          <t>Población que se ha vacunado de la gripe en la última campaña (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>246929; 302932</t>
+          <t>248290; 305099</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>309030; 371751</t>
+          <t>315295; 378285</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>232451; 281921</t>
+          <t>232316; 282363</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>259760; 301967</t>
+          <t>259606; 304226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>356441; 423980</t>
+          <t>356895; 422080</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>413583; 486670</t>
+          <t>414286; 485067</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>319968; 386981</t>
+          <t>324798; 385997</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>466434; 507548</t>
+          <t>464662; 508203</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>623242; 709817</t>
+          <t>621604; 706206</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>743416; 834106</t>
+          <t>744513; 841965</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>567974; 652224</t>
+          <t>567499; 651165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>739509; 799327</t>
+          <t>738271; 800948</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>99101; 142403</t>
+          <t>97422; 141309</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>183140; 241298</t>
+          <t>181174; 239456</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>188290; 244034</t>
+          <t>189323; 245463</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>349645; 577249</t>
+          <t>348641; 576670</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80557; 121769</t>
+          <t>80187; 120988</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132142; 184696</t>
+          <t>132649; 184477</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>173240; 233231</t>
+          <t>176164; 236099</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>561342; 1130854</t>
+          <t>562251; 1103221</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>190074; 247422</t>
+          <t>189468; 246013</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>330244; 406482</t>
+          <t>330078; 404835</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377434; 457440</t>
+          <t>377890; 456032</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1031853; 1723127</t>
+          <t>1024464; 1735781</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48200; 78484</t>
+          <t>47511; 79370</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39893; 71512</t>
+          <t>38406; 68174</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46395; 76987</t>
+          <t>43631; 75268</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>189203; 240572</t>
+          <t>191326; 241420</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32892; 59500</t>
+          <t>33392; 58386</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30371; 56808</t>
+          <t>30189; 57961</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42778; 72251</t>
+          <t>41866; 71556</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>185075; 225096</t>
+          <t>185062; 225990</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>89230; 130873</t>
+          <t>89181; 130106</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75602; 116689</t>
+          <t>74627; 118121</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>96354; 140036</t>
+          <t>94522; 137758</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>387021; 454630</t>
+          <t>390940; 452380</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>415220; 490166</t>
+          <t>417913; 490096</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>559132; 653680</t>
+          <t>560136; 649726</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>487594; 575651</t>
+          <t>490665; 570476</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>772265; 1098645</t>
+          <t>765679; 1092943</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>491392; 576847</t>
+          <t>494083; 574991</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>604630; 701873</t>
+          <t>602752; 696557</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>564447; 655983</t>
+          <t>563781; 660200</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1265437; 1832578</t>
+          <t>1268417; 1861979</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>936157; 1051755</t>
+          <t>933527; 1045896</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1185392; 1319694</t>
+          <t>1187017; 1320952</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1075348; 1205669</t>
+          <t>1076388; 1203837</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2172940; 2887364</t>
+          <t>2171809; 2896188</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P37-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P37-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,07; 29,57</t>
+          <t>24,2; 29,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,38; 38,85</t>
+          <t>31,96; 37,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,8; 37,43</t>
+          <t>30,73; 37,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,42; 59,08</t>
+          <t>48,15; 56,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,14; 32,09</t>
+          <t>27,17; 32,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,97; 36,26</t>
+          <t>31,02; 36,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,65; 38,81</t>
+          <t>32,23; 38,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,69; 67,48</t>
+          <t>61,85; 67,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,49; 30,09</t>
+          <t>26,59; 30,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,21; 36,43</t>
+          <t>32,26; 36,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,45; 37,23</t>
+          <t>32,52; 37,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,22; 63,16</t>
+          <t>56,98; 61,89</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,35</t>
+          <t>5,74; 8,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 12,21</t>
+          <t>9,25; 12,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 11,82</t>
+          <t>9,15; 11,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 25,18</t>
+          <t>22,96; 26,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 7,63</t>
+          <t>5,18; 7,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 10,5</t>
+          <t>7,62; 10,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 11,87</t>
+          <t>8,7; 11,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,12; 49,3</t>
+          <t>25,11; 28,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 7,5</t>
+          <t>5,71; 7,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 10,89</t>
+          <t>8,79; 10,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,3; 11,22</t>
+          <t>9,37; 11,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,62; 38,33</t>
+          <t>24,6; 27,17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 14,42</t>
+          <t>8,59; 14,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 14,2</t>
+          <t>8,2; 14,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,98; 13,76</t>
+          <t>8,16; 13,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,59; 37,34</t>
+          <t>29,34; 36,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 12,26</t>
+          <t>7,11; 12,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 12,64</t>
+          <t>6,24; 12,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 13,03</t>
+          <t>7,78; 13,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,02; 34,22</t>
+          <t>28,1; 33,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 12,67</t>
+          <t>8,61; 12,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,58</t>
+          <t>7,97; 12,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,62; 12,57</t>
+          <t>8,66; 12,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,91; 34,61</t>
+          <t>29,69; 34,17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,76; 14,97</t>
+          <t>12,72; 15,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,4; 19,03</t>
+          <t>16,38; 19,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,53; 16,89</t>
+          <t>14,44; 17,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,18; 31,66</t>
+          <t>29,31; 32,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,63; 17,03</t>
+          <t>14,51; 17,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 19,6</t>
+          <t>16,97; 19,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,96; 18,69</t>
+          <t>16,04; 18,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,74; 50,99</t>
+          <t>34,66; 37,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,03; 15,72</t>
+          <t>14,02; 15,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 18,96</t>
+          <t>17,0; 18,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,58; 17,42</t>
+          <t>15,53; 17,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,57; 40,77</t>
+          <t>32,45; 34,58</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281191</t>
+          <t>300817</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>488370</t>
+          <t>530239</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>769562</t>
+          <t>831057</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>248290; 305099</t>
+          <t>249696; 305252</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>315295; 378285</t>
+          <t>311206; 369256</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>232316; 282363</t>
+          <t>231829; 280752</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>259606; 304226</t>
+          <t>278574; 325379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>356895; 422080</t>
+          <t>357355; 424126</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>414286; 485067</t>
+          <t>414964; 485253</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>324798; 385997</t>
+          <t>320591; 385822</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>464662; 508203</t>
+          <t>508004; 551935</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>621604; 706206</t>
+          <t>624059; 710917</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>744513; 841965</t>
+          <t>745711; 839029</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>567499; 651165</t>
+          <t>568726; 651676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>738271; 800948</t>
+          <t>797625; 866323</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504076</t>
+          <t>553150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>732865</t>
+          <t>582396</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1236941</t>
+          <t>1135546</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97422; 141309</t>
+          <t>97178; 141906</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>181174; 239456</t>
+          <t>181408; 237231</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>189323; 245463</t>
+          <t>189946; 246904</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>348641; 576670</t>
+          <t>512117; 598381</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80187; 120988</t>
+          <t>82089; 120265</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132649; 184477</t>
+          <t>133944; 183954</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>176164; 236099</t>
+          <t>173041; 232489</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>562251; 1103221</t>
+          <t>545310; 616559</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>189468; 246013</t>
+          <t>187110; 246986</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>330078; 404835</t>
+          <t>326735; 405608</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377890; 456032</t>
+          <t>381004; 459846</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1024464; 1735781</t>
+          <t>1082941; 1195995</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215525</t>
+          <t>233900</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>204094</t>
+          <t>227893</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>419620</t>
+          <t>461793</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47511; 79370</t>
+          <t>47270; 78177</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38406; 68174</t>
+          <t>39384; 70038</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43631; 75268</t>
+          <t>44651; 74448</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>191326; 241420</t>
+          <t>208799; 260222</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33392; 58386</t>
+          <t>33860; 58938</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30189; 57961</t>
+          <t>28622; 56736</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41866; 71556</t>
+          <t>42698; 72876</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>185062; 225990</t>
+          <t>206484; 249642</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>89181; 130106</t>
+          <t>88466; 128900</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74627; 118121</t>
+          <t>74861; 113945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94522; 137758</t>
+          <t>94887; 138338</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>390940; 452380</t>
+          <t>429469; 494300</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1000793</t>
+          <t>1087867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1425330</t>
+          <t>1340529</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2426123</t>
+          <t>2428396</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>417913; 490096</t>
+          <t>416507; 494851</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>560136; 649726</t>
+          <t>559477; 656442</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>490665; 570476</t>
+          <t>487887; 575024</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>765679; 1092943</t>
+          <t>1031834; 1146053</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>494083; 574991</t>
+          <t>490061; 578056</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>602752; 696557</t>
+          <t>602926; 698836</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>563781; 660200</t>
+          <t>566482; 661705</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1268417; 1861979</t>
+          <t>1291981; 1391189</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933527; 1045896</t>
+          <t>932541; 1048028</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1187017; 1320952</t>
+          <t>1184716; 1316580</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1076388; 1203837</t>
+          <t>1072875; 1205437</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2171809; 2896188</t>
+          <t>2351770; 2506792</t>
         </is>
       </c>
     </row>
